--- a/output/pdf_financials_xlsx/ABND.xlsx
+++ b/output/pdf_financials_xlsx/ABND.xlsx
@@ -2768,7 +2768,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.08641</v>
       </c>

--- a/output/pdf_financials_xlsx/ABND.xlsx
+++ b/output/pdf_financials_xlsx/ABND.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.058564</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004735</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002953</v>
       </c>
     </row>
     <row r="13">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.625477</v>
+        <v>-7.684041</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.152652</v>
+        <v>-3.157387</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.152652</v>
+        <v>-3.155605</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.625477</v>
+        <v>-7.684041</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.152652</v>
+        <v>-3.157387</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.152652</v>
+        <v>-3.155605</v>
       </c>
     </row>
     <row r="30">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-3753.157142857142</v>
+        <v>-3758.794047619047</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-70371.69642857143</v>
+        <v>-70437.61160714286</v>
       </c>
     </row>
     <row r="31">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.202445</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007212</v>
       </c>
     </row>
     <row r="35">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.202445</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.007212</v>
       </c>
     </row>
     <row r="37">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.388855</v>
+        <v>0.18641</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.151474</v>
+        <v>0.148102</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.054984</v>
+        <v>0.047772</v>
       </c>
     </row>
     <row r="49">
@@ -2409,13 +2409,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.390945</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.262555</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.204398</v>
       </c>
     </row>
     <row r="125">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.390945</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.262555</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.204398</v>
       </c>
     </row>
     <row r="126">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3957,7 +3957,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.390945</v>
       </c>
@@ -4889,7 +4893,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/ABND.xlsx
+++ b/output/pdf_financials_xlsx/ABND.xlsx
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.079221</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.079221</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-5.454062</v>
+        <v>-5.533283</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.597752</v>
+        <v>-0.604752</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.418083</v>
@@ -3744,7 +3744,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>-0.079221</v>
       </c>
@@ -3868,7 +3872,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.537625</v>
       </c>
